--- a/online_sales.xlsx
+++ b/online_sales.xlsx
@@ -10,13 +10,26 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="76" documentId="8_{40DC3F9B-B119-4A5A-8465-FC6386182E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D992E8-73CF-4A96-8E11-BF85598A0D3D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{69F4FE3B-8D7D-4A85-87E9-C9D340C32163}"/>
+    <workbookView minimized="1" xWindow="2784" yWindow="4164" windowWidth="2388" windowHeight="564" activeTab="1" xr2:uid="{69F4FE3B-8D7D-4A85-87E9-C9D340C32163}"/>
   </bookViews>
   <sheets>
     <sheet name="online_sales" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1285,13 +1298,6 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$1:$A$3</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>(Sheet1!$A$1,Sheet1!$A$3)</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
@@ -1302,25 +1308,20 @@
                   <c:v>$810,270.94 </c:v>
                 </c:pt>
               </c:strCache>
+              <c:extLst/>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$3:$B$3</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>Sheet1!$A$3</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)">
+                <c:pt idx="0">
                   <c:v>810270.94</c:v>
                 </c:pt>
               </c:numCache>
+              <c:extLst/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -1355,13 +1356,6 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$1:$A$3</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>(Sheet1!$A$1,Sheet1!$A$3)</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
@@ -1369,34 +1363,20 @@
                   <c:v>performance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>$3,143,787.73 </c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>$810,270.94 </c:v>
                 </c:pt>
               </c:strCache>
+              <c:extLst/>
             </c:strRef>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{F5D05F6E-A05E-4728-AFD3-386EB277150F}">
-                  <c16:filteredLitCache>
-                    <c:numCache>
-                      <c:ptCount val="0"/>
-                    </c:numCache>
-                  </c16:filteredLitCache>
-                </c:ext>
-              </c:extLst>
-              <c:f/>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2700,10 +2680,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
